--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31360" windowHeight="15060"/>
+    <workbookView windowHeight="17460"/>
   </bookViews>
   <sheets>
     <sheet name="减脂日记" sheetId="1" r:id="rId1"/>
@@ -2665,14 +2665,16 @@
       <c r="B54" t="s">
         <v>17</v>
       </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F54" s="4" t="str">
+      <c r="D54" s="4">
+        <v>77.55</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.15</v>
+      </c>
+      <c r="F54" s="4">
         <f>IF(D54="","",ROUND(D7-D54,2))</f>
-        <v/>
+        <v>10.5</v>
       </c>
     </row>
     <row r="55" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17460"/>
+    <workbookView windowWidth="31360" windowHeight="15060"/>
   </bookViews>
   <sheets>
     <sheet name="减脂日记" sheetId="1" r:id="rId1"/>
@@ -384,7 +384,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,13 +395,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -860,148 +853,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2684,14 +2677,16 @@
       <c r="B55" t="s">
         <v>20</v>
       </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F55" s="4" t="str">
+      <c r="D55" s="4">
+        <v>77.5</v>
+      </c>
+      <c r="E55" s="4">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="F55" s="4">
         <f>IF(D55="","",ROUND(D7-D55,2))</f>
-        <v/>
+        <v>10.55</v>
       </c>
     </row>
     <row r="56" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -2696,14 +2696,16 @@
       <c r="B56" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F56" s="4" t="str">
+      <c r="D56" s="4">
+        <v>77.1</v>
+      </c>
+      <c r="E56" s="4">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="F56" s="4">
         <f>IF(D56="","",ROUND(D7-D56,2))</f>
-        <v/>
+        <v>10.95</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2713,14 +2715,16 @@
       <c r="B57" t="s">
         <v>8</v>
       </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F57" s="4" t="str">
+      <c r="D57" s="4">
+        <v>76.5</v>
+      </c>
+      <c r="E57" s="4">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="F57" s="4">
         <f>IF(D57="","",ROUND(D7-D57,2))</f>
-        <v/>
+        <v>11.55</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2730,14 +2734,16 @@
       <c r="B58" t="s">
         <v>11</v>
       </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F58" s="4" t="str">
+      <c r="D58" s="4">
+        <v>77</v>
+      </c>
+      <c r="E58" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.5</v>
+      </c>
+      <c r="F58" s="4">
         <f>IF(D58="","",ROUND(D7-D58,2))</f>
-        <v/>
+        <v>11.05</v>
       </c>
     </row>
     <row r="59" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31360" windowHeight="15060"/>
+    <workbookView windowWidth="31360" windowHeight="15660"/>
   </bookViews>
   <sheets>
     <sheet name="减脂日记" sheetId="1" r:id="rId1"/>
@@ -2753,14 +2753,16 @@
       <c r="B59" t="s">
         <v>13</v>
       </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F59" s="4" t="str">
+      <c r="D59" s="4">
+        <v>77.35</v>
+      </c>
+      <c r="E59" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.35</v>
+      </c>
+      <c r="F59" s="4">
         <f>IF(D59="","",ROUND(D7-D59,2))</f>
-        <v/>
+        <v>10.7</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2770,14 +2772,16 @@
       <c r="B60" t="s">
         <v>25</v>
       </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F60" s="4" t="str">
+      <c r="D60" s="4">
+        <v>76.3</v>
+      </c>
+      <c r="E60" s="4">
+        <f t="shared" si="0"/>
+        <v>1.05</v>
+      </c>
+      <c r="F60" s="4">
         <f>IF(D60="","",ROUND(D7-D60,2))</f>
-        <v/>
+        <v>11.75</v>
       </c>
     </row>
     <row r="61" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -2791,14 +2791,16 @@
       <c r="B61" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F61" s="4" t="str">
+      <c r="D61" s="4">
+        <v>75.65</v>
+      </c>
+      <c r="E61" s="4">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="F61" s="4">
         <f>IF(D61="","",ROUND(D7-D61,2))</f>
-        <v/>
+        <v>12.4</v>
       </c>
     </row>
     <row r="62" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31360" windowHeight="15660"/>
+    <workbookView windowHeight="17460"/>
   </bookViews>
   <sheets>
     <sheet name="减脂日记" sheetId="1" r:id="rId1"/>
@@ -2810,14 +2810,16 @@
       <c r="B62" t="s">
         <v>20</v>
       </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F62" s="4" t="str">
+      <c r="D62" s="4">
+        <v>76.4</v>
+      </c>
+      <c r="E62" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.75</v>
+      </c>
+      <c r="F62" s="4">
         <f>IF(D62="","",ROUND(D7-D62,2))</f>
-        <v/>
+        <v>11.65</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2827,14 +2829,16 @@
       <c r="B63" t="s">
         <v>15</v>
       </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F63" s="4" t="str">
+      <c r="D63" s="4">
+        <v>76.15</v>
+      </c>
+      <c r="E63" s="4">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="F63" s="4">
         <f>IF(D63="","",ROUND(D7-D63,2))</f>
-        <v/>
+        <v>11.9</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2844,14 +2848,16 @@
       <c r="B64" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F64" s="4" t="str">
+      <c r="D64" s="4">
+        <v>77.05</v>
+      </c>
+      <c r="E64" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.9</v>
+      </c>
+      <c r="F64" s="4">
         <f>IF(D64="","",ROUND(D7-D64,2))</f>
-        <v/>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2861,14 +2867,16 @@
       <c r="B65" t="s">
         <v>11</v>
       </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F65" s="4" t="str">
+      <c r="D65" s="4">
+        <v>76.7</v>
+      </c>
+      <c r="E65" s="4">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="F65" s="4">
         <f>IF(D65="","",ROUND(D7-D65,2))</f>
-        <v/>
+        <v>11.35</v>
       </c>
     </row>
     <row r="66" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17460"/>
+    <workbookView windowWidth="31360" windowHeight="15060"/>
   </bookViews>
   <sheets>
     <sheet name="减脂日记" sheetId="1" r:id="rId1"/>
@@ -2886,14 +2886,16 @@
       <c r="B66" t="s">
         <v>13</v>
       </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F66" s="4" t="str">
+      <c r="D66" s="4">
+        <v>75.6</v>
+      </c>
+      <c r="E66" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1</v>
+      </c>
+      <c r="F66" s="4">
         <f>IF(D66="","",ROUND(D7-D66,2))</f>
-        <v/>
+        <v>12.45</v>
       </c>
     </row>
     <row r="67" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31360" windowHeight="15060"/>
+    <workbookView windowWidth="31360" windowHeight="15660"/>
   </bookViews>
   <sheets>
     <sheet name="减脂日记" sheetId="1" r:id="rId1"/>
@@ -2905,14 +2905,16 @@
       <c r="B67" t="s">
         <v>25</v>
       </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4" t="str">
+      <c r="D67" s="4">
+        <v>75.25</v>
+      </c>
+      <c r="E67" s="4">
         <f t="shared" ref="E67:E79" si="1">IF(OR(D67="",D66=""),"",ROUND(D66-D67,2))</f>
-        <v/>
-      </c>
-      <c r="F67" s="4" t="str">
+        <v>0.35</v>
+      </c>
+      <c r="F67" s="4">
         <f>IF(D67="","",ROUND(D7-D67,2))</f>
-        <v/>
+        <v>12.8</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2922,14 +2924,16 @@
       <c r="B68" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4" t="str">
+      <c r="D68" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="E68" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F68" s="4" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="F68" s="4">
         <f>IF(D68="","",ROUND(D7-D68,2))</f>
-        <v/>
+        <v>12.85</v>
       </c>
     </row>
     <row r="69" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -2943,14 +2943,16 @@
       <c r="B69" t="s">
         <v>20</v>
       </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4" t="str">
+      <c r="D69" s="4">
+        <v>75.05</v>
+      </c>
+      <c r="E69" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F69" s="4" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="F69" s="4">
         <f>IF(D69="","",ROUND(D7-D69,2))</f>
-        <v/>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -2962,14 +2962,16 @@
       <c r="B70" t="s">
         <v>15</v>
       </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4" t="str">
+      <c r="D70" s="4">
+        <v>74.65</v>
+      </c>
+      <c r="E70" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F70" s="4" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="F70" s="4">
         <f>IF(D70="","",ROUND(D7-D70,2))</f>
-        <v/>
+        <v>13.4</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2979,14 +2981,16 @@
       <c r="B71" t="s">
         <v>8</v>
       </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4" t="str">
+      <c r="D71" s="4">
+        <v>75.5</v>
+      </c>
+      <c r="E71" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F71" s="4" t="str">
+        <v>-0.85</v>
+      </c>
+      <c r="F71" s="4">
         <f>IF(D71="","",ROUND(D7-D71,2))</f>
-        <v/>
+        <v>12.55</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2996,14 +3000,16 @@
       <c r="B72" t="s">
         <v>11</v>
       </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4" t="str">
+      <c r="D72" s="4">
+        <v>74.86</v>
+      </c>
+      <c r="E72" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F72" s="4" t="str">
+        <v>0.64</v>
+      </c>
+      <c r="F72" s="4">
         <f>IF(D72="","",ROUND(D7-D72,2))</f>
-        <v/>
+        <v>13.19</v>
       </c>
     </row>
     <row r="73" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -3001,15 +3001,15 @@
         <v>11</v>
       </c>
       <c r="D72" s="4">
-        <v>74.86</v>
+        <v>74.85</v>
       </c>
       <c r="E72" s="4">
         <f t="shared" si="1"/>
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="F72" s="4">
         <f>IF(D72="","",ROUND(D7-D72,2))</f>
-        <v>13.19</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3019,14 +3019,16 @@
       <c r="B73" t="s">
         <v>13</v>
       </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4" t="str">
+      <c r="D73" s="4">
+        <v>74.7</v>
+      </c>
+      <c r="E73" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F73" s="4" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="F73" s="4">
         <f>IF(D73="","",ROUND(D7-D73,2))</f>
-        <v/>
+        <v>13.35</v>
       </c>
     </row>
     <row r="74" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -3038,14 +3038,16 @@
       <c r="B74" t="s">
         <v>25</v>
       </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4" t="str">
+      <c r="D74" s="4">
+        <v>74.05</v>
+      </c>
+      <c r="E74" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F74" s="4" t="str">
+        <v>0.65</v>
+      </c>
+      <c r="F74" s="4">
         <f>IF(D74="","",ROUND(D7-D74,2))</f>
-        <v/>
+        <v>14</v>
       </c>
     </row>
     <row r="75" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -3057,14 +3057,16 @@
       <c r="B75" t="s">
         <v>17</v>
       </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4" t="str">
+      <c r="D75" s="4">
+        <v>73.7</v>
+      </c>
+      <c r="E75" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F75" s="4" t="str">
+        <v>0.35</v>
+      </c>
+      <c r="F75" s="4">
         <f>IF(D75="","",ROUND(D7-D75,2))</f>
-        <v/>
+        <v>14.35</v>
       </c>
     </row>
     <row r="76" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -3076,14 +3076,16 @@
       <c r="B76" t="s">
         <v>20</v>
       </c>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4" t="str">
+      <c r="D76" s="4">
+        <v>74.4</v>
+      </c>
+      <c r="E76" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F76" s="4" t="str">
+        <v>-0.7</v>
+      </c>
+      <c r="F76" s="4">
         <f>IF(D76="","",ROUND(D7-D76,2))</f>
-        <v/>
+        <v>13.65</v>
       </c>
     </row>
     <row r="77" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -3095,14 +3095,16 @@
       <c r="B77" t="s">
         <v>15</v>
       </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4" t="str">
+      <c r="D77" s="4">
+        <v>74.45</v>
+      </c>
+      <c r="E77" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F77" s="4" t="str">
+        <v>-0.05</v>
+      </c>
+      <c r="F77" s="4">
         <f>IF(D77="","",ROUND(D7-D77,2))</f>
-        <v/>
+        <v>13.6</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3112,14 +3114,16 @@
       <c r="B78" t="s">
         <v>8</v>
       </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4" t="str">
+      <c r="D78" s="4">
+        <v>75.2</v>
+      </c>
+      <c r="E78" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F78" s="4" t="str">
+        <v>-0.75</v>
+      </c>
+      <c r="F78" s="4">
         <f>IF(D78="","",ROUND(D7-D78,2))</f>
-        <v/>
+        <v>12.85</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3129,14 +3133,16 @@
       <c r="B79" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4" t="str">
+      <c r="D79" s="4">
+        <v>75.75</v>
+      </c>
+      <c r="E79" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F79" s="4" t="str">
+        <v>-0.55</v>
+      </c>
+      <c r="F79" s="4">
         <f>IF(D79="","",ROUND(D7-D79,2))</f>
-        <v/>
+        <v>12.3</v>
       </c>
     </row>
   </sheetData>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3299,16 +3299,16 @@
       <c r="C82" t="s">
         <v>9</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" s="4" t="str">
+      <c r="D82" s="4">
+        <v>73.85</v>
+      </c>
+      <c r="E82" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F82" s="4" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="F82" s="4">
         <f>IF(D82="","",ROUND(D7-D82,2))</f>
-        <v/>
+        <v>14.2</v>
       </c>
       <c r="G82" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3324,16 +3324,16 @@
       <c r="C83" t="s">
         <v>9</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" s="4" t="str">
+      <c r="D83" s="4">
+        <v>73.7</v>
+      </c>
+      <c r="E83" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F83" s="4" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="F83" s="4">
         <f>IF(D83="","",ROUND(D7-D83,2))</f>
-        <v/>
+        <v>14.35</v>
       </c>
       <c r="G83" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3349,16 +3349,16 @@
       <c r="C84" t="s">
         <v>9</v>
       </c>
-      <c r="D84" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="4" t="str">
+      <c r="D84" s="4">
+        <v>73.05</v>
+      </c>
+      <c r="E84" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F84" s="4" t="str">
+        <v>0.65</v>
+      </c>
+      <c r="F84" s="4">
         <f>IF(D84="","",ROUND(D7-D84,2))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="G84" t="s">
         <v>9</v>
@@ -3374,16 +3374,16 @@
       <c r="C85" t="s">
         <v>9</v>
       </c>
-      <c r="D85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="4" t="str">
+      <c r="D85" s="4">
+        <v>74.8</v>
+      </c>
+      <c r="E85" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F85" s="4" t="str">
+        <v>-1.75</v>
+      </c>
+      <c r="F85" s="4">
         <f>IF(D85="","",ROUND(D7-D85,2))</f>
-        <v/>
+        <v>13.25</v>
       </c>
       <c r="G85" t="s">
         <v>9</v>
@@ -3399,16 +3399,16 @@
       <c r="C86" t="s">
         <v>9</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="4" t="str">
+      <c r="D86" s="4">
+        <v>75.55</v>
+      </c>
+      <c r="E86" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F86" s="4" t="str">
+        <v>-0.75</v>
+      </c>
+      <c r="F86" s="4">
         <f>IF(D86="","",ROUND(D7-D86,2))</f>
-        <v/>
+        <v>12.5</v>
       </c>
       <c r="G86" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3424,16 +3424,16 @@
       <c r="C87" t="s">
         <v>9</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" s="4" t="str">
+      <c r="D87" s="4">
+        <v>73.4</v>
+      </c>
+      <c r="E87" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F87" s="4" t="str">
+        <v>2.15</v>
+      </c>
+      <c r="F87" s="4">
         <f>IF(D87="","",ROUND(D7-D87,2))</f>
-        <v/>
+        <v>14.65</v>
       </c>
       <c r="G87" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3449,16 +3449,16 @@
       <c r="C88" t="s">
         <v>9</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="4" t="str">
+      <c r="D88" s="4">
+        <v>73.6</v>
+      </c>
+      <c r="E88" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F88" s="4" t="str">
+        <v>-0.2</v>
+      </c>
+      <c r="F88" s="4">
         <f>IF(D88="","",ROUND(D7-D88,2))</f>
-        <v/>
+        <v>14.45</v>
       </c>
       <c r="G88" t="s">
         <v>9</v>
@@ -3474,16 +3474,16 @@
       <c r="C89" t="s">
         <v>9</v>
       </c>
-      <c r="D89" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E89" s="4" t="str">
+      <c r="D89" s="4">
+        <v>72.9</v>
+      </c>
+      <c r="E89" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F89" s="4" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="F89" s="4">
         <f>IF(D89="","",ROUND(D7-D89,2))</f>
-        <v/>
+        <v>15.15</v>
       </c>
       <c r="G89" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3499,16 +3499,16 @@
       <c r="C90" t="s">
         <v>9</v>
       </c>
-      <c r="D90" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E90" s="4" t="str">
+      <c r="D90" s="4">
+        <v>73.2</v>
+      </c>
+      <c r="E90" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F90" s="4" t="str">
+        <v>-0.3</v>
+      </c>
+      <c r="F90" s="4">
         <f>IF(D90="","",ROUND(D7-D90,2))</f>
-        <v/>
+        <v>14.85</v>
       </c>
       <c r="G90" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3524,16 +3524,16 @@
       <c r="C91" t="s">
         <v>9</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="4" t="str">
+      <c r="D91" s="4">
+        <v>72.7</v>
+      </c>
+      <c r="E91" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F91" s="4" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="F91" s="4">
         <f>IF(D91="","",ROUND(D7-D91,2))</f>
-        <v/>
+        <v>15.35</v>
       </c>
       <c r="G91" t="s">
         <v>9</v>
@@ -3549,16 +3549,16 @@
       <c r="C92" t="s">
         <v>9</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="4" t="str">
+      <c r="D92" s="4">
+        <v>74</v>
+      </c>
+      <c r="E92" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F92" s="4" t="str">
+        <v>-1.3</v>
+      </c>
+      <c r="F92" s="4">
         <f>IF(D92="","",ROUND(D7-D92,2))</f>
-        <v/>
+        <v>14.05</v>
       </c>
       <c r="G92" t="s">
         <v>9</v>
@@ -3574,16 +3574,16 @@
       <c r="C93" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E93" s="4" t="str">
+      <c r="D93" s="4">
+        <v>73.9</v>
+      </c>
+      <c r="E93" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F93" s="4" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="F93" s="4">
         <f>IF(D93="","",ROUND(D7-D93,2))</f>
-        <v/>
+        <v>14.15</v>
       </c>
       <c r="G93" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3599,16 +3599,16 @@
       <c r="C94" t="s">
         <v>9</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E94" s="4" t="str">
+      <c r="D94" s="4">
+        <v>73.1</v>
+      </c>
+      <c r="E94" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F94" s="4" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="F94" s="4">
         <f>IF(D94="","",ROUND(D7-D94,2))</f>
-        <v/>
+        <v>14.95</v>
       </c>
       <c r="G94" t="s">
         <v>9</v>
@@ -3624,16 +3624,16 @@
       <c r="C95" t="s">
         <v>9</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="4" t="str">
+      <c r="D95" s="4">
+        <v>73.55</v>
+      </c>
+      <c r="E95" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F95" s="4" t="str">
+        <v>-0.45</v>
+      </c>
+      <c r="F95" s="4">
         <f>IF(D95="","",ROUND(D7-D95,2))</f>
-        <v/>
+        <v>14.5</v>
       </c>
       <c r="G95" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3649,16 +3649,16 @@
       <c r="C96" t="s">
         <v>9</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="4" t="str">
+      <c r="D96" s="4">
+        <v>73.35</v>
+      </c>
+      <c r="E96" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F96" s="4" t="str">
+        <v>0.2</v>
+      </c>
+      <c r="F96" s="4">
         <f>IF(D96="","",ROUND(D7-D96,2))</f>
-        <v/>
+        <v>14.7</v>
       </c>
       <c r="G96" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3674,16 +3674,16 @@
       <c r="C97" t="s">
         <v>9</v>
       </c>
-      <c r="D97" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E97" s="4" t="str">
+      <c r="D97" s="4">
+        <v>74.5</v>
+      </c>
+      <c r="E97" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F97" s="4" t="str">
+        <v>-1.15</v>
+      </c>
+      <c r="F97" s="4">
         <f>IF(D97="","",ROUND(D7-D97,2))</f>
-        <v/>
+        <v>13.55</v>
       </c>
       <c r="G97" t="s">
         <v>9</v>
@@ -3699,16 +3699,16 @@
       <c r="C98" t="s">
         <v>9</v>
       </c>
-      <c r="D98" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="4" t="str">
+      <c r="D98" s="4">
+        <v>74.6</v>
+      </c>
+      <c r="E98" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F98" s="4" t="str">
+        <v>-0.1</v>
+      </c>
+      <c r="F98" s="4">
         <f>IF(D98="","",ROUND(D7-D98,2))</f>
-        <v/>
+        <v>13.45</v>
       </c>
       <c r="G98" t="s">
         <v>9</v>
@@ -3724,16 +3724,16 @@
       <c r="C99" t="s">
         <v>9</v>
       </c>
-      <c r="D99" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E99" s="4" t="str">
+      <c r="D99" s="4">
+        <v>73.9</v>
+      </c>
+      <c r="E99" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F99" s="4" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="F99" s="4">
         <f>IF(D99="","",ROUND(D7-D99,2))</f>
-        <v/>
+        <v>14.15</v>
       </c>
       <c r="G99" t="s">
         <v>9</v>
@@ -3749,16 +3749,16 @@
       <c r="C100" t="s">
         <v>9</v>
       </c>
-      <c r="D100" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E100" s="4" t="str">
+      <c r="D100" s="4">
+        <v>72.95</v>
+      </c>
+      <c r="E100" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F100" s="4" t="str">
+        <v>0.95</v>
+      </c>
+      <c r="F100" s="4">
         <f>IF(D100="","",ROUND(D7-D100,2))</f>
-        <v/>
+        <v>15.1</v>
       </c>
       <c r="G100" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3774,16 +3774,16 @@
       <c r="C101" t="s">
         <v>9</v>
       </c>
-      <c r="D101" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E101" s="4" t="str">
+      <c r="D101" s="4">
+        <v>72.25</v>
+      </c>
+      <c r="E101" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F101" s="4" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="F101" s="4">
         <f>IF(D101="","",ROUND(D7-D101,2))</f>
-        <v/>
+        <v>15.8</v>
       </c>
       <c r="G101" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3799,16 +3799,16 @@
       <c r="C102" t="s">
         <v>9</v>
       </c>
-      <c r="D102" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="4" t="str">
+      <c r="D102" s="4">
+        <v>71.8</v>
+      </c>
+      <c r="E102" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F102" s="4" t="str">
+        <v>0.45</v>
+      </c>
+      <c r="F102" s="4">
         <f>IF(D102="","",ROUND(D7-D102,2))</f>
-        <v/>
+        <v>16.25</v>
       </c>
       <c r="G102" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3824,16 +3824,16 @@
       <c r="C103" t="s">
         <v>9</v>
       </c>
-      <c r="D103" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E103" s="4" t="str">
+      <c r="D103" s="4">
+        <v>72.75</v>
+      </c>
+      <c r="E103" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F103" s="4" t="str">
+        <v>-0.95</v>
+      </c>
+      <c r="F103" s="4">
         <f>IF(D103="","",ROUND(D7-D103,2))</f>
-        <v/>
+        <v>15.3</v>
       </c>
       <c r="G103" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3849,16 +3849,16 @@
       <c r="C104" t="s">
         <v>9</v>
       </c>
-      <c r="D104" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E104" s="4" t="str">
+      <c r="D104" s="4">
+        <v>71.9</v>
+      </c>
+      <c r="E104" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F104" s="4" t="str">
+        <v>0.85</v>
+      </c>
+      <c r="F104" s="4">
         <f>IF(D104="","",ROUND(D7-D104,2))</f>
-        <v/>
+        <v>16.15</v>
       </c>
       <c r="G104" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3874,16 +3874,16 @@
       <c r="C105" t="s">
         <v>9</v>
       </c>
-      <c r="D105" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E105" s="4" t="str">
+      <c r="D105" s="4">
+        <v>73.05</v>
+      </c>
+      <c r="E105" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F105" s="4" t="str">
+        <v>-1.15</v>
+      </c>
+      <c r="F105" s="4">
         <f>IF(D105="","",ROUND(D7-D105,2))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
         <v>9</v>
@@ -3899,16 +3899,16 @@
       <c r="C106" t="s">
         <v>9</v>
       </c>
-      <c r="D106" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="4" t="str">
+      <c r="D106" s="4">
+        <v>74</v>
+      </c>
+      <c r="E106" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F106" s="4" t="str">
+        <v>-0.95</v>
+      </c>
+      <c r="F106" s="4">
         <f>IF(D106="","",ROUND(D7-D106,2))</f>
-        <v/>
+        <v>14.05</v>
       </c>
       <c r="G106" t="s">
         <v>9</v>
@@ -3924,16 +3924,16 @@
       <c r="C107" t="s">
         <v>9</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="4" t="str">
+      <c r="D107" s="4">
+        <v>74.35</v>
+      </c>
+      <c r="E107" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F107" s="4" t="str">
+        <v>-0.35</v>
+      </c>
+      <c r="F107" s="4">
         <f>IF(D107="","",ROUND(D7-D107,2))</f>
-        <v/>
+        <v>13.7</v>
       </c>
       <c r="G107" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="144">
   <si>
     <t>日期</t>
   </si>
@@ -3949,16 +3949,16 @@
       <c r="C108" t="s">
         <v>9</v>
       </c>
-      <c r="D108" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="4" t="str">
+      <c r="D108" s="4">
+        <v>73.75</v>
+      </c>
+      <c r="E108" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F108" s="4" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="F108" s="4">
         <f>IF(D108="","",ROUND(D7-D108,2))</f>
-        <v/>
+        <v>14.3</v>
       </c>
       <c r="G108" t="s">
         <v>9</v>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="236">
   <si>
     <t>日期</t>
   </si>
@@ -462,6 +462,282 @@
   </si>
   <si>
     <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>2026-07-04</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>2026-07-11</t>
+  </si>
+  <si>
+    <t>2026-07-12</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-02</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-09</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>2026-08-23</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+  <si>
+    <t>2026-08-30</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>2026-09-05</t>
+  </si>
+  <si>
+    <t>2026-09-06</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>2026-09-08</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-12</t>
+  </si>
+  <si>
+    <t>2026-09-13</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
+    <t>2026-09-19</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-09-22</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
   </si>
 </sst>
 </file>
@@ -3974,22 +4250,28 @@
       <c r="C109" t="s">
         <v>9</v>
       </c>
-      <c r="D109" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="4" t="str">
+      <c r="D109" s="4">
+        <v>73.95</v>
+      </c>
+      <c r="E109" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F109" s="4" t="str">
+        <v>-0.2</v>
+      </c>
+      <c r="F109" s="4">
         <f>IF(D109="","",ROUND(D7-D109,2))</f>
-        <v/>
+        <v>14.1</v>
       </c>
       <c r="G109" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="5:6">
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>144</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
       <c r="E110" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3999,7 +4281,13 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="5:6">
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>145</v>
+      </c>
+      <c r="B111" t="s">
+        <v>20</v>
+      </c>
       <c r="E111" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4009,7 +4297,13 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="5:6">
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>146</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
       <c r="E112" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4019,7 +4313,13 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="5:6">
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>147</v>
+      </c>
+      <c r="B113" t="s">
+        <v>8</v>
+      </c>
       <c r="E113" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4029,7 +4329,13 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="5:6">
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>148</v>
+      </c>
+      <c r="B114" t="s">
+        <v>11</v>
+      </c>
       <c r="E114" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4039,7 +4345,13 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="5:6">
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" t="s">
+        <v>13</v>
+      </c>
       <c r="E115" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4049,7 +4361,13 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="5:6">
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>150</v>
+      </c>
+      <c r="B116" t="s">
+        <v>25</v>
+      </c>
       <c r="E116" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4059,7 +4377,13 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="5:6">
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>151</v>
+      </c>
+      <c r="B117" t="s">
+        <v>17</v>
+      </c>
       <c r="E117" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4069,7 +4393,13 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="5:6">
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>152</v>
+      </c>
+      <c r="B118" t="s">
+        <v>20</v>
+      </c>
       <c r="E118" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4079,7 +4409,13 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="5:6">
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>153</v>
+      </c>
+      <c r="B119" t="s">
+        <v>15</v>
+      </c>
       <c r="E119" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4089,7 +4425,13 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="5:6">
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>154</v>
+      </c>
+      <c r="B120" t="s">
+        <v>8</v>
+      </c>
       <c r="E120" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4099,7 +4441,13 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="5:6">
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>155</v>
+      </c>
+      <c r="B121" t="s">
+        <v>11</v>
+      </c>
       <c r="E121" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4109,7 +4457,13 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="5:6">
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>156</v>
+      </c>
+      <c r="B122" t="s">
+        <v>13</v>
+      </c>
       <c r="E122" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4119,7 +4473,13 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="5:6">
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>157</v>
+      </c>
+      <c r="B123" t="s">
+        <v>25</v>
+      </c>
       <c r="E123" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4129,7 +4489,13 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="5:6">
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>158</v>
+      </c>
+      <c r="B124" t="s">
+        <v>17</v>
+      </c>
       <c r="E124" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4139,7 +4505,13 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="5:6">
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>159</v>
+      </c>
+      <c r="B125" t="s">
+        <v>20</v>
+      </c>
       <c r="E125" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4149,7 +4521,13 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="5:6">
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>160</v>
+      </c>
+      <c r="B126" t="s">
+        <v>15</v>
+      </c>
       <c r="E126" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4159,7 +4537,13 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="5:6">
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>161</v>
+      </c>
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
       <c r="E127" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4169,7 +4553,13 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="5:6">
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>162</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
       <c r="E128" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4179,7 +4569,13 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="5:6">
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>163</v>
+      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
       <c r="E129" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4189,7 +4585,13 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="5:6">
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>164</v>
+      </c>
+      <c r="B130" t="s">
+        <v>25</v>
+      </c>
       <c r="E130" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4199,7 +4601,13 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="5:6">
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>165</v>
+      </c>
+      <c r="B131" t="s">
+        <v>17</v>
+      </c>
       <c r="E131" t="str">
         <f t="shared" ref="E131:E194" si="2">IF(OR(D131="",D130=""),"",ROUND(D130-D131,2))</f>
         <v/>
@@ -4209,7 +4617,13 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="5:6">
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>166</v>
+      </c>
+      <c r="B132" t="s">
+        <v>20</v>
+      </c>
       <c r="E132" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4219,7 +4633,13 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="5:6">
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>167</v>
+      </c>
+      <c r="B133" t="s">
+        <v>15</v>
+      </c>
       <c r="E133" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4229,7 +4649,13 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="5:6">
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>168</v>
+      </c>
+      <c r="B134" t="s">
+        <v>8</v>
+      </c>
       <c r="E134" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4239,7 +4665,13 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="5:6">
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>169</v>
+      </c>
+      <c r="B135" t="s">
+        <v>11</v>
+      </c>
       <c r="E135" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4249,7 +4681,13 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="5:6">
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>170</v>
+      </c>
+      <c r="B136" t="s">
+        <v>13</v>
+      </c>
       <c r="E136" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4259,7 +4697,13 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="5:6">
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>171</v>
+      </c>
+      <c r="B137" t="s">
+        <v>25</v>
+      </c>
       <c r="E137" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4269,7 +4713,13 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="5:6">
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>172</v>
+      </c>
+      <c r="B138" t="s">
+        <v>17</v>
+      </c>
       <c r="E138" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4279,7 +4729,13 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="5:6">
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>173</v>
+      </c>
+      <c r="B139" t="s">
+        <v>20</v>
+      </c>
       <c r="E139" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4289,7 +4745,13 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="5:6">
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>174</v>
+      </c>
+      <c r="B140" t="s">
+        <v>15</v>
+      </c>
       <c r="E140" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4299,7 +4761,13 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="5:6">
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>175</v>
+      </c>
+      <c r="B141" t="s">
+        <v>8</v>
+      </c>
       <c r="E141" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4309,7 +4777,13 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="5:6">
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>176</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
       <c r="E142" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4319,7 +4793,13 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="5:6">
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>177</v>
+      </c>
+      <c r="B143" t="s">
+        <v>13</v>
+      </c>
       <c r="E143" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4329,7 +4809,13 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="5:6">
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>178</v>
+      </c>
+      <c r="B144" t="s">
+        <v>25</v>
+      </c>
       <c r="E144" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4339,7 +4825,13 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="5:6">
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>179</v>
+      </c>
+      <c r="B145" t="s">
+        <v>17</v>
+      </c>
       <c r="E145" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4349,7 +4841,13 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="5:6">
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>180</v>
+      </c>
+      <c r="B146" t="s">
+        <v>20</v>
+      </c>
       <c r="E146" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4359,7 +4857,13 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="5:6">
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>181</v>
+      </c>
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
       <c r="E147" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4369,7 +4873,13 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="5:6">
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>182</v>
+      </c>
+      <c r="B148" t="s">
+        <v>8</v>
+      </c>
       <c r="E148" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4379,7 +4889,13 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="5:6">
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>183</v>
+      </c>
+      <c r="B149" t="s">
+        <v>11</v>
+      </c>
       <c r="E149" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4389,7 +4905,13 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="5:6">
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>184</v>
+      </c>
+      <c r="B150" t="s">
+        <v>13</v>
+      </c>
       <c r="E150" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4399,7 +4921,13 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="5:6">
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>185</v>
+      </c>
+      <c r="B151" t="s">
+        <v>25</v>
+      </c>
       <c r="E151" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4409,7 +4937,13 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="5:6">
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>186</v>
+      </c>
+      <c r="B152" t="s">
+        <v>17</v>
+      </c>
       <c r="E152" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4419,7 +4953,13 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="5:6">
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>187</v>
+      </c>
+      <c r="B153" t="s">
+        <v>20</v>
+      </c>
       <c r="E153" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4429,7 +4969,13 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="5:6">
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>188</v>
+      </c>
+      <c r="B154" t="s">
+        <v>15</v>
+      </c>
       <c r="E154" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4439,7 +4985,13 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="5:6">
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>189</v>
+      </c>
+      <c r="B155" t="s">
+        <v>8</v>
+      </c>
       <c r="E155" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4449,7 +5001,13 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="5:6">
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>190</v>
+      </c>
+      <c r="B156" t="s">
+        <v>11</v>
+      </c>
       <c r="E156" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4459,7 +5017,13 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="5:6">
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>191</v>
+      </c>
+      <c r="B157" t="s">
+        <v>13</v>
+      </c>
       <c r="E157" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4469,7 +5033,13 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="5:6">
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>192</v>
+      </c>
+      <c r="B158" t="s">
+        <v>25</v>
+      </c>
       <c r="E158" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4479,7 +5049,13 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="5:6">
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>193</v>
+      </c>
+      <c r="B159" t="s">
+        <v>17</v>
+      </c>
       <c r="E159" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4489,7 +5065,13 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="5:6">
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>194</v>
+      </c>
+      <c r="B160" t="s">
+        <v>20</v>
+      </c>
       <c r="E160" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4499,7 +5081,13 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="5:6">
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>195</v>
+      </c>
+      <c r="B161" t="s">
+        <v>15</v>
+      </c>
       <c r="E161" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4509,7 +5097,13 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="5:6">
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>196</v>
+      </c>
+      <c r="B162" t="s">
+        <v>8</v>
+      </c>
       <c r="E162" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4519,7 +5113,13 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="5:6">
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>197</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
       <c r="E163" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4529,7 +5129,13 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="5:6">
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>198</v>
+      </c>
+      <c r="B164" t="s">
+        <v>13</v>
+      </c>
       <c r="E164" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4539,7 +5145,13 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="5:6">
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>199</v>
+      </c>
+      <c r="B165" t="s">
+        <v>25</v>
+      </c>
       <c r="E165" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4549,7 +5161,13 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="5:6">
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>200</v>
+      </c>
+      <c r="B166" t="s">
+        <v>17</v>
+      </c>
       <c r="E166" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4559,7 +5177,13 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="5:6">
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>201</v>
+      </c>
+      <c r="B167" t="s">
+        <v>20</v>
+      </c>
       <c r="E167" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4569,7 +5193,13 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="5:6">
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>202</v>
+      </c>
+      <c r="B168" t="s">
+        <v>15</v>
+      </c>
       <c r="E168" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4579,7 +5209,13 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="5:6">
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>203</v>
+      </c>
+      <c r="B169" t="s">
+        <v>8</v>
+      </c>
       <c r="E169" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4589,7 +5225,13 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="5:6">
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>204</v>
+      </c>
+      <c r="B170" t="s">
+        <v>11</v>
+      </c>
       <c r="E170" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4599,7 +5241,13 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="5:6">
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>205</v>
+      </c>
+      <c r="B171" t="s">
+        <v>13</v>
+      </c>
       <c r="E171" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4609,7 +5257,13 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="5:6">
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>206</v>
+      </c>
+      <c r="B172" t="s">
+        <v>25</v>
+      </c>
       <c r="E172" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4619,7 +5273,13 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="5:6">
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>207</v>
+      </c>
+      <c r="B173" t="s">
+        <v>17</v>
+      </c>
       <c r="E173" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4629,7 +5289,13 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="5:6">
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>208</v>
+      </c>
+      <c r="B174" t="s">
+        <v>20</v>
+      </c>
       <c r="E174" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4639,7 +5305,13 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="5:6">
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>209</v>
+      </c>
+      <c r="B175" t="s">
+        <v>15</v>
+      </c>
       <c r="E175" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4649,7 +5321,13 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="5:6">
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>210</v>
+      </c>
+      <c r="B176" t="s">
+        <v>8</v>
+      </c>
       <c r="E176" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4659,7 +5337,13 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="5:6">
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>211</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
       <c r="E177" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4669,7 +5353,13 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="5:6">
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>212</v>
+      </c>
+      <c r="B178" t="s">
+        <v>13</v>
+      </c>
       <c r="E178" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4679,7 +5369,13 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="5:6">
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>213</v>
+      </c>
+      <c r="B179" t="s">
+        <v>25</v>
+      </c>
       <c r="E179" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4689,7 +5385,13 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="5:6">
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>214</v>
+      </c>
+      <c r="B180" t="s">
+        <v>17</v>
+      </c>
       <c r="E180" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4699,7 +5401,13 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="5:6">
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>215</v>
+      </c>
+      <c r="B181" t="s">
+        <v>20</v>
+      </c>
       <c r="E181" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4709,7 +5417,13 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="5:6">
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>216</v>
+      </c>
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
       <c r="E182" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4719,7 +5433,13 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="5:6">
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>217</v>
+      </c>
+      <c r="B183" t="s">
+        <v>8</v>
+      </c>
       <c r="E183" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4729,7 +5449,13 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="5:6">
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>218</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
       <c r="E184" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4739,7 +5465,13 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="5:6">
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>219</v>
+      </c>
+      <c r="B185" t="s">
+        <v>13</v>
+      </c>
       <c r="E185" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4749,7 +5481,13 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="5:6">
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>220</v>
+      </c>
+      <c r="B186" t="s">
+        <v>25</v>
+      </c>
       <c r="E186" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4759,7 +5497,13 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="5:6">
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>221</v>
+      </c>
+      <c r="B187" t="s">
+        <v>17</v>
+      </c>
       <c r="E187" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4769,7 +5513,13 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="5:6">
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>222</v>
+      </c>
+      <c r="B188" t="s">
+        <v>20</v>
+      </c>
       <c r="E188" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4779,7 +5529,13 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="5:6">
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>223</v>
+      </c>
+      <c r="B189" t="s">
+        <v>15</v>
+      </c>
       <c r="E189" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4789,7 +5545,13 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="5:6">
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>224</v>
+      </c>
+      <c r="B190" t="s">
+        <v>8</v>
+      </c>
       <c r="E190" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4799,7 +5561,13 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="5:6">
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>225</v>
+      </c>
+      <c r="B191" t="s">
+        <v>11</v>
+      </c>
       <c r="E191" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4809,7 +5577,13 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="5:6">
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>226</v>
+      </c>
+      <c r="B192" t="s">
+        <v>13</v>
+      </c>
       <c r="E192" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4819,7 +5593,13 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="5:6">
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>227</v>
+      </c>
+      <c r="B193" t="s">
+        <v>25</v>
+      </c>
       <c r="E193" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4829,7 +5609,13 @@
         <v/>
       </c>
     </row>
-    <row r="194" spans="5:6">
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>228</v>
+      </c>
+      <c r="B194" t="s">
+        <v>17</v>
+      </c>
       <c r="E194" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -4839,7 +5625,13 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="5:6">
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>229</v>
+      </c>
+      <c r="B195" t="s">
+        <v>20</v>
+      </c>
       <c r="E195" t="str">
         <f t="shared" ref="E195:E258" si="3">IF(OR(D195="",D194=""),"",ROUND(D194-D195,2))</f>
         <v/>
@@ -4849,7 +5641,13 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="5:6">
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>230</v>
+      </c>
+      <c r="B196" t="s">
+        <v>15</v>
+      </c>
       <c r="E196" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4859,7 +5657,13 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="5:6">
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>231</v>
+      </c>
+      <c r="B197" t="s">
+        <v>8</v>
+      </c>
       <c r="E197" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4869,7 +5673,13 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="5:6">
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>232</v>
+      </c>
+      <c r="B198" t="s">
+        <v>11</v>
+      </c>
       <c r="E198" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4879,7 +5689,13 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="5:6">
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>233</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
       <c r="E199" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4889,7 +5705,13 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="5:6">
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>234</v>
+      </c>
+      <c r="B200" t="s">
+        <v>25</v>
+      </c>
       <c r="E200" t="str">
         <f t="shared" si="3"/>
         <v/>
@@ -4899,7 +5721,13 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="5:6">
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>235</v>
+      </c>
+      <c r="B201" t="s">
+        <v>17</v>
+      </c>
       <c r="E201" t="str">
         <f t="shared" si="3"/>
         <v/>

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4272,13 +4272,16 @@
       <c r="B110" t="s">
         <v>17</v>
       </c>
-      <c r="E110" t="str">
+      <c r="D110">
+        <v>72.6</v>
+      </c>
+      <c r="E110">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F110" t="str">
+        <v>1.35</v>
+      </c>
+      <c r="F110">
         <f>IF(D110="","",ROUND(D7-D110,2))</f>
-        <v/>
+        <v>15.45</v>
       </c>
     </row>
     <row r="111" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4291,13 +4291,16 @@
       <c r="B111" t="s">
         <v>20</v>
       </c>
-      <c r="E111" t="str">
+      <c r="D111">
+        <v>71.65</v>
+      </c>
+      <c r="E111">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F111" t="str">
+        <v>0.95</v>
+      </c>
+      <c r="F111">
         <f>IF(D111="","",ROUND(D7-D111,2))</f>
-        <v/>
+        <v>16.4</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -4307,13 +4310,16 @@
       <c r="B112" t="s">
         <v>15</v>
       </c>
-      <c r="E112" t="str">
+      <c r="D112">
+        <v>73.6</v>
+      </c>
+      <c r="E112">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F112" t="str">
+        <v>-1.95</v>
+      </c>
+      <c r="F112">
         <f>IF(D112="","",ROUND(D7-D112,2))</f>
-        <v/>
+        <v>14.45</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -4323,13 +4329,16 @@
       <c r="B113" t="s">
         <v>8</v>
       </c>
-      <c r="E113" t="str">
+      <c r="D113">
+        <v>73.5</v>
+      </c>
+      <c r="E113">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F113" t="str">
+        <v>0.1</v>
+      </c>
+      <c r="F113">
         <f>IF(D113="","",ROUND(D7-D113,2))</f>
-        <v/>
+        <v>14.55</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4339,13 +4348,16 @@
       <c r="B114" t="s">
         <v>11</v>
       </c>
-      <c r="E114" t="str">
+      <c r="D114">
+        <v>74.2</v>
+      </c>
+      <c r="E114">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F114" t="str">
+        <v>-0.7</v>
+      </c>
+      <c r="F114">
         <f>IF(D114="","",ROUND(D7-D114,2))</f>
-        <v/>
+        <v>13.85</v>
       </c>
     </row>
     <row r="115" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4367,13 +4367,16 @@
       <c r="B115" t="s">
         <v>13</v>
       </c>
-      <c r="E115" t="str">
+      <c r="D115">
+        <v>72.15</v>
+      </c>
+      <c r="E115">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F115" t="str">
+        <v>2.05</v>
+      </c>
+      <c r="F115">
         <f>IF(D115="","",ROUND(D7-D115,2))</f>
-        <v/>
+        <v>15.9</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4383,13 +4386,16 @@
       <c r="B116" t="s">
         <v>25</v>
       </c>
-      <c r="E116" t="str">
+      <c r="D116">
+        <v>71.6</v>
+      </c>
+      <c r="E116">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F116" t="str">
+        <v>0.55</v>
+      </c>
+      <c r="F116">
         <f>IF(D116="","",ROUND(D7-D116,2))</f>
-        <v/>
+        <v>16.45</v>
       </c>
     </row>
     <row r="117" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4405,13 +4405,16 @@
       <c r="B117" t="s">
         <v>17</v>
       </c>
-      <c r="E117" t="str">
+      <c r="D117">
+        <v>71.1</v>
+      </c>
+      <c r="E117">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F117" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="F117">
         <f>IF(D117="","",ROUND(D7-D117,2))</f>
-        <v/>
+        <v>16.95</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4421,13 +4424,16 @@
       <c r="B118" t="s">
         <v>20</v>
       </c>
-      <c r="E118" t="str">
+      <c r="D118">
+        <v>71.95</v>
+      </c>
+      <c r="E118">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F118" t="str">
+        <v>-0.85</v>
+      </c>
+      <c r="F118">
         <f>IF(D118="","",ROUND(D7-D118,2))</f>
-        <v/>
+        <v>16.1</v>
       </c>
     </row>
     <row r="119" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4443,13 +4443,16 @@
       <c r="B119" t="s">
         <v>15</v>
       </c>
-      <c r="E119" t="str">
+      <c r="D119">
+        <v>72.55</v>
+      </c>
+      <c r="E119">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F119" t="str">
+        <v>-0.6</v>
+      </c>
+      <c r="F119">
         <f>IF(D119="","",ROUND(D7-D119,2))</f>
-        <v/>
+        <v>15.5</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4459,13 +4462,16 @@
       <c r="B120" t="s">
         <v>8</v>
       </c>
-      <c r="E120" t="str">
+      <c r="D120">
+        <v>73.55</v>
+      </c>
+      <c r="E120">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F120" t="str">
+        <v>-1</v>
+      </c>
+      <c r="F120">
         <f>IF(D120="","",ROUND(D7-D120,2))</f>
-        <v/>
+        <v>14.5</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -4475,13 +4481,16 @@
       <c r="B121" t="s">
         <v>11</v>
       </c>
-      <c r="E121" t="str">
+      <c r="D121">
+        <v>74.55</v>
+      </c>
+      <c r="E121">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F121" t="str">
+        <v>-1</v>
+      </c>
+      <c r="F121">
         <f>IF(D121="","",ROUND(D7-D121,2))</f>
-        <v/>
+        <v>13.5</v>
       </c>
     </row>
     <row r="122" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4500,13 +4500,16 @@
       <c r="B122" t="s">
         <v>13</v>
       </c>
-      <c r="E122" t="str">
+      <c r="D122">
+        <v>72.75</v>
+      </c>
+      <c r="E122">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F122" t="str">
+        <v>1.8</v>
+      </c>
+      <c r="F122">
         <f>IF(D122="","",ROUND(D7-D122,2))</f>
-        <v/>
+        <v>15.3</v>
       </c>
     </row>
     <row r="123" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4519,13 +4519,16 @@
       <c r="B123" t="s">
         <v>25</v>
       </c>
-      <c r="E123" t="str">
+      <c r="D123">
+        <v>72.15</v>
+      </c>
+      <c r="E123">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F123" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="F123">
         <f>IF(D123="","",ROUND(D7-D123,2))</f>
-        <v/>
+        <v>15.9</v>
       </c>
     </row>
     <row r="124" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4538,13 +4538,16 @@
       <c r="B124" t="s">
         <v>17</v>
       </c>
-      <c r="E124" t="str">
+      <c r="D124">
+        <v>71.65</v>
+      </c>
+      <c r="E124">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F124" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="F124">
         <f>IF(D124="","",ROUND(D7-D124,2))</f>
-        <v/>
+        <v>16.4</v>
       </c>
     </row>
     <row r="125" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4557,13 +4557,16 @@
       <c r="B125" t="s">
         <v>20</v>
       </c>
-      <c r="E125" t="str">
+      <c r="D125">
+        <v>71.4</v>
+      </c>
+      <c r="E125">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F125" t="str">
+        <v>0.25</v>
+      </c>
+      <c r="F125">
         <f>IF(D125="","",ROUND(D7-D125,2))</f>
-        <v/>
+        <v>16.65</v>
       </c>
     </row>
     <row r="126" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4576,13 +4576,16 @@
       <c r="B126" t="s">
         <v>15</v>
       </c>
-      <c r="E126" t="str">
+      <c r="D126">
+        <v>72</v>
+      </c>
+      <c r="E126">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F126" t="str">
+        <v>-0.6</v>
+      </c>
+      <c r="F126">
         <f>IF(D126="","",ROUND(D7-D126,2))</f>
-        <v/>
+        <v>16.05</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -4592,13 +4595,16 @@
       <c r="B127" t="s">
         <v>8</v>
       </c>
-      <c r="E127" t="str">
+      <c r="D127">
+        <v>73</v>
+      </c>
+      <c r="E127">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F127" t="str">
+        <v>-1</v>
+      </c>
+      <c r="F127">
         <f>IF(D127="","",ROUND(D7-D127,2))</f>
-        <v/>
+        <v>15.05</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4608,13 +4614,16 @@
       <c r="B128" t="s">
         <v>11</v>
       </c>
-      <c r="E128" t="str">
+      <c r="D128">
+        <v>74</v>
+      </c>
+      <c r="E128">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F128" t="str">
+        <v>-1</v>
+      </c>
+      <c r="F128">
         <f>IF(D128="","",ROUND(D7-D128,2))</f>
-        <v/>
+        <v>14.05</v>
       </c>
     </row>
     <row r="129" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4633,13 +4633,16 @@
       <c r="B129" t="s">
         <v>13</v>
       </c>
-      <c r="E129" t="str">
+      <c r="D129">
+        <v>72.05</v>
+      </c>
+      <c r="E129">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F129" t="str">
+        <v>1.95</v>
+      </c>
+      <c r="F129">
         <f>IF(D129="","",ROUND(D7-D129,2))</f>
-        <v/>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4652,13 +4652,16 @@
       <c r="B130" t="s">
         <v>25</v>
       </c>
-      <c r="E130" t="str">
+      <c r="D130">
+        <v>71.45</v>
+      </c>
+      <c r="E130">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F130" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="F130">
         <f>IF(D130="","",ROUND(D7-D130,2))</f>
-        <v/>
+        <v>16.6</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4668,13 +4671,16 @@
       <c r="B131" t="s">
         <v>17</v>
       </c>
-      <c r="E131" t="str">
+      <c r="D131">
+        <v>71.3</v>
+      </c>
+      <c r="E131">
         <f t="shared" ref="E131:E194" si="2">IF(OR(D131="",D130=""),"",ROUND(D130-D131,2))</f>
-        <v/>
-      </c>
-      <c r="F131" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="F131">
         <f>IF(D131="","",ROUND(D7-D131,2))</f>
-        <v/>
+        <v>16.75</v>
       </c>
     </row>
     <row r="132" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4690,13 +4690,16 @@
       <c r="B132" t="s">
         <v>20</v>
       </c>
-      <c r="E132" t="str">
+      <c r="D132">
+        <v>71.7</v>
+      </c>
+      <c r="E132">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F132" t="str">
+        <v>-0.4</v>
+      </c>
+      <c r="F132">
         <f>IF(D132="","",ROUND(D7-D132,2))</f>
-        <v/>
+        <v>16.35</v>
       </c>
     </row>
     <row r="133" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4709,13 +4709,16 @@
       <c r="B133" t="s">
         <v>15</v>
       </c>
-      <c r="E133" t="str">
+      <c r="D133">
+        <v>73.5</v>
+      </c>
+      <c r="E133">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F133" t="str">
+        <v>-1.8</v>
+      </c>
+      <c r="F133">
         <f>IF(D133="","",ROUND(D7-D133,2))</f>
-        <v/>
+        <v>14.55</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4725,13 +4728,16 @@
       <c r="B134" t="s">
         <v>8</v>
       </c>
-      <c r="E134" t="str">
+      <c r="D134">
+        <v>73.7</v>
+      </c>
+      <c r="E134">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F134" t="str">
+        <v>-0.2</v>
+      </c>
+      <c r="F134">
         <f>IF(D134="","",ROUND(D7-D134,2))</f>
-        <v/>
+        <v>14.35</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4741,13 +4747,16 @@
       <c r="B135" t="s">
         <v>11</v>
       </c>
-      <c r="E135" t="str">
+      <c r="D135">
+        <v>73.85</v>
+      </c>
+      <c r="E135">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F135" t="str">
+        <v>-0.15</v>
+      </c>
+      <c r="F135">
         <f>IF(D135="","",ROUND(D7-D135,2))</f>
-        <v/>
+        <v>14.2</v>
       </c>
     </row>
     <row r="136" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4766,13 +4766,16 @@
       <c r="B136" t="s">
         <v>13</v>
       </c>
-      <c r="E136" t="str">
+      <c r="D136">
+        <v>71.8</v>
+      </c>
+      <c r="E136">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F136" t="str">
+        <v>2.05</v>
+      </c>
+      <c r="F136">
         <f>IF(D136="","",ROUND(D7-D136,2))</f>
-        <v/>
+        <v>16.25</v>
       </c>
     </row>
     <row r="137" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4785,13 +4785,16 @@
       <c r="B137" t="s">
         <v>25</v>
       </c>
-      <c r="E137" t="str">
+      <c r="D137">
+        <v>71.2</v>
+      </c>
+      <c r="E137">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F137" t="str">
+        <v>0.6</v>
+      </c>
+      <c r="F137">
         <f>IF(D137="","",ROUND(D7-D137,2))</f>
-        <v/>
+        <v>16.85</v>
       </c>
     </row>
     <row r="138" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4804,13 +4804,16 @@
       <c r="B138" t="s">
         <v>17</v>
       </c>
-      <c r="E138" t="str">
+      <c r="D138">
+        <v>71.15</v>
+      </c>
+      <c r="E138">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F138" t="str">
+        <v>0.05</v>
+      </c>
+      <c r="F138">
         <f>IF(D138="","",ROUND(D7-D138,2))</f>
-        <v/>
+        <v>16.9</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4820,13 +4823,16 @@
       <c r="B139" t="s">
         <v>20</v>
       </c>
-      <c r="E139" t="str">
+      <c r="D139">
+        <v>70.85</v>
+      </c>
+      <c r="E139">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F139" t="str">
+        <v>0.3</v>
+      </c>
+      <c r="F139">
         <f>IF(D139="","",ROUND(D7-D139,2))</f>
-        <v/>
+        <v>17.2</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4836,13 +4842,16 @@
       <c r="B140" t="s">
         <v>15</v>
       </c>
-      <c r="E140" t="str">
+      <c r="D140">
+        <v>72</v>
+      </c>
+      <c r="E140">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F140" t="str">
+        <v>-1.15</v>
+      </c>
+      <c r="F140">
         <f>IF(D140="","",ROUND(D7-D140,2))</f>
-        <v/>
+        <v>16.05</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4852,13 +4861,16 @@
       <c r="B141" t="s">
         <v>8</v>
       </c>
-      <c r="E141" t="str">
+      <c r="D141">
+        <v>73.5</v>
+      </c>
+      <c r="E141">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F141" t="str">
+        <v>-1.5</v>
+      </c>
+      <c r="F141">
         <f>IF(D141="","",ROUND(D7-D141,2))</f>
-        <v/>
+        <v>14.55</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4868,13 +4880,16 @@
       <c r="B142" t="s">
         <v>11</v>
       </c>
-      <c r="E142" t="str">
+      <c r="D142">
+        <v>74.3</v>
+      </c>
+      <c r="E142">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F142" t="str">
+        <v>-0.8</v>
+      </c>
+      <c r="F142">
         <f>IF(D142="","",ROUND(D7-D142,2))</f>
-        <v/>
+        <v>13.75</v>
       </c>
     </row>
     <row r="143" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4899,13 +4899,16 @@
       <c r="B143" t="s">
         <v>13</v>
       </c>
-      <c r="E143" t="str">
+      <c r="D143">
+        <v>72.95</v>
+      </c>
+      <c r="E143">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F143" t="str">
+        <v>1.35</v>
+      </c>
+      <c r="F143">
         <f>IF(D143="","",ROUND(D7-D143,2))</f>
-        <v/>
+        <v>15.1</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4915,13 +4918,16 @@
       <c r="B144" t="s">
         <v>25</v>
       </c>
-      <c r="E144" t="str">
+      <c r="D144">
+        <v>71.55</v>
+      </c>
+      <c r="E144">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F144" t="str">
+        <v>1.4</v>
+      </c>
+      <c r="F144">
         <f>IF(D144="","",ROUND(D7-D144,2))</f>
-        <v/>
+        <v>16.5</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4931,13 +4937,16 @@
       <c r="B145" t="s">
         <v>17</v>
       </c>
-      <c r="E145" t="str">
+      <c r="D145">
+        <v>71.8</v>
+      </c>
+      <c r="E145">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F145" t="str">
+        <v>-0.25</v>
+      </c>
+      <c r="F145">
         <f>IF(D145="","",ROUND(D7-D145,2))</f>
-        <v/>
+        <v>16.25</v>
       </c>
     </row>
     <row r="146" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -4956,13 +4956,16 @@
       <c r="B146" t="s">
         <v>20</v>
       </c>
-      <c r="E146" t="str">
+      <c r="D146">
+        <v>72.8</v>
+      </c>
+      <c r="E146">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F146" t="str">
+        <v>-1</v>
+      </c>
+      <c r="F146">
         <f>IF(D146="","",ROUND(D7-D146,2))</f>
-        <v/>
+        <v>15.25</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4972,13 +4975,16 @@
       <c r="B147" t="s">
         <v>15</v>
       </c>
-      <c r="E147" t="str">
+      <c r="D147">
+        <v>73.2</v>
+      </c>
+      <c r="E147">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F147" t="str">
+        <v>-0.4</v>
+      </c>
+      <c r="F147">
         <f>IF(D147="","",ROUND(D7-D147,2))</f>
-        <v/>
+        <v>14.85</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4988,13 +4994,16 @@
       <c r="B148" t="s">
         <v>8</v>
       </c>
-      <c r="E148" t="str">
+      <c r="D148">
+        <v>73.5</v>
+      </c>
+      <c r="E148">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F148" t="str">
+        <v>-0.3</v>
+      </c>
+      <c r="F148">
         <f>IF(D148="","",ROUND(D7-D148,2))</f>
-        <v/>
+        <v>14.55</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -5004,13 +5013,16 @@
       <c r="B149" t="s">
         <v>11</v>
       </c>
-      <c r="E149" t="str">
+      <c r="D149">
+        <v>74</v>
+      </c>
+      <c r="E149">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F149" t="str">
+        <v>-0.5</v>
+      </c>
+      <c r="F149">
         <f>IF(D149="","",ROUND(D7-D149,2))</f>
-        <v/>
+        <v>14.05</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -5020,13 +5032,16 @@
       <c r="B150" t="s">
         <v>13</v>
       </c>
-      <c r="E150" t="str">
+      <c r="D150">
+        <v>74.2</v>
+      </c>
+      <c r="E150">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F150" t="str">
+        <v>-0.2</v>
+      </c>
+      <c r="F150">
         <f>IF(D150="","",ROUND(D7-D150,2))</f>
-        <v/>
+        <v>13.85</v>
       </c>
     </row>
     <row r="151" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -5051,13 +5051,16 @@
       <c r="B151" t="s">
         <v>25</v>
       </c>
-      <c r="E151" t="str">
+      <c r="D151">
+        <v>73.15</v>
+      </c>
+      <c r="E151">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F151" t="str">
+        <v>1.05</v>
+      </c>
+      <c r="F151">
         <f>IF(D151="","",ROUND(D7-D151,2))</f>
-        <v/>
+        <v>14.9</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -5067,13 +5070,16 @@
       <c r="B152" t="s">
         <v>17</v>
       </c>
-      <c r="E152" t="str">
+      <c r="D152">
+        <v>74.4</v>
+      </c>
+      <c r="E152">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F152" t="str">
+        <v>-1.25</v>
+      </c>
+      <c r="F152">
         <f>IF(D152="","",ROUND(D7-D152,2))</f>
-        <v/>
+        <v>13.65</v>
       </c>
     </row>
     <row r="153" spans="1:6">

--- a/08-life/小胖子减脂日记.xlsx
+++ b/08-life/小胖子减脂日记.xlsx
@@ -5089,13 +5089,16 @@
       <c r="B153" t="s">
         <v>20</v>
       </c>
-      <c r="E153" t="str">
+      <c r="D153">
+        <v>74.45</v>
+      </c>
+      <c r="E153">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F153" t="str">
+        <v>-0.05</v>
+      </c>
+      <c r="F153">
         <f>IF(D153="","",ROUND(D7-D153,2))</f>
-        <v/>
+        <v>13.6</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -5105,13 +5108,16 @@
       <c r="B154" t="s">
         <v>15</v>
       </c>
-      <c r="E154" t="str">
+      <c r="D154">
+        <v>74.5</v>
+      </c>
+      <c r="E154">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F154" t="str">
+        <v>-0.05</v>
+      </c>
+      <c r="F154">
         <f>IF(D154="","",ROUND(D7-D154,2))</f>
-        <v/>
+        <v>13.55</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -5121,13 +5127,16 @@
       <c r="B155" t="s">
         <v>8</v>
       </c>
-      <c r="E155" t="str">
+      <c r="D155">
+        <v>74.8</v>
+      </c>
+      <c r="E155">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F155" t="str">
+        <v>-0.3</v>
+      </c>
+      <c r="F155">
         <f>IF(D155="","",ROUND(D7-D155,2))</f>
-        <v/>
+        <v>13.25</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5137,13 +5146,16 @@
       <c r="B156" t="s">
         <v>11</v>
       </c>
-      <c r="E156" t="str">
+      <c r="D156">
+        <v>75</v>
+      </c>
+      <c r="E156">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F156" t="str">
+        <v>-0.2</v>
+      </c>
+      <c r="F156">
         <f>IF(D156="","",ROUND(D7-D156,2))</f>
-        <v/>
+        <v>13.05</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -5153,13 +5165,16 @@
       <c r="B157" t="s">
         <v>13</v>
       </c>
-      <c r="E157" t="str">
+      <c r="D157">
+        <v>72.9</v>
+      </c>
+      <c r="E157">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="F157" t="str">
+        <v>2.1</v>
+      </c>
+      <c r="F157">
         <f>IF(D157="","",ROUND(D7-D157,2))</f>
-        <v/>
+        <v>15.15</v>
       </c>
     </row>
     <row r="158" spans="1:6">
